--- a/data/Format=XLSX/Model=M10+/Floor=2/Location=Unit 210/Device=04/M10+_device04_10-13-2024 15:09:55.xlsx
+++ b/data/Format=XLSX/Model=M10+/Floor=2/Location=Unit 210/Device=04/M10+_device04_10-13-2024 15:09:55.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Downloads/M10+_device04_10-13-2024 15:09:"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Developer/Personal/Trellis Air Quality/trellis-aq/data/Format=XLSX/Model=M10+/Floor=2/Location=Unit 210/Device=04/M10+_device04_10-13-2024 15:09:"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EBB9D7-7102-854C-BC0C-EE3A1380FE22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E068E50B-3AE5-4A46-9A11-8AAA45870A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="880" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="561">
   <si>
     <t>NO.</t>
   </si>
@@ -1336,15 +1336,6 @@
     <t>2024-10-13 14:00:00(+08:00)</t>
   </si>
   <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>2024-10-13 15:00:00(+08:00)</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
     <t>AQI</t>
   </si>
   <si>
@@ -1625,9 +1616,6 @@
   </si>
   <si>
     <t>578</t>
-  </si>
-  <si>
-    <t>577</t>
   </si>
   <si>
     <t>TVOC</t>
@@ -2066,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -2090,19 +2078,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2119,13 +2107,13 @@
         <v>187</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>161</v>
@@ -2145,13 +2133,13 @@
         <v>178</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>170</v>
@@ -2171,13 +2159,13 @@
         <v>170</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>168</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>170</v>
@@ -2197,13 +2185,13 @@
         <v>170</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>170</v>
@@ -2223,13 +2211,13 @@
         <v>170</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>79</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>170</v>
@@ -2249,13 +2237,13 @@
         <v>170</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>173</v>
@@ -2275,13 +2263,13 @@
         <v>173</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>99</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>173</v>
@@ -2301,13 +2289,13 @@
         <v>173</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>104</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>173</v>
@@ -2327,13 +2315,13 @@
         <v>170</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>106</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>173</v>
@@ -2353,13 +2341,13 @@
         <v>156</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>173</v>
@@ -2379,13 +2367,13 @@
         <v>148</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>173</v>
@@ -2405,13 +2393,13 @@
         <v>126</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>170</v>
@@ -2431,13 +2419,13 @@
         <v>116</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>170</v>
@@ -2457,13 +2445,13 @@
         <v>76</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>170</v>
@@ -2483,13 +2471,13 @@
         <v>64</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>170</v>
@@ -2509,13 +2497,13 @@
         <v>73</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>170</v>
@@ -2535,13 +2523,13 @@
         <v>93</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>170</v>
@@ -2561,13 +2549,13 @@
         <v>104</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>170</v>
@@ -2587,13 +2575,13 @@
         <v>212</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>170</v>
@@ -2613,13 +2601,13 @@
         <v>221</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>148</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>170</v>
@@ -2639,13 +2627,13 @@
         <v>221</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>170</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>168</v>
@@ -2665,13 +2653,13 @@
         <v>204</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>168</v>
@@ -2691,13 +2679,13 @@
         <v>190</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>343</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>168</v>
@@ -2717,13 +2705,13 @@
         <v>178</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>168</v>
@@ -2743,13 +2731,13 @@
         <v>168</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>181</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>170</v>
@@ -2769,13 +2757,13 @@
         <v>163</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>138</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>168</v>
@@ -2795,13 +2783,13 @@
         <v>158</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>168</v>
@@ -2821,13 +2809,13 @@
         <v>145</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>106</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>168</v>
@@ -2847,13 +2835,13 @@
         <v>138</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>168</v>
@@ -2873,13 +2861,13 @@
         <v>138</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>168</v>
@@ -2899,13 +2887,13 @@
         <v>143</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>170</v>
@@ -2925,13 +2913,13 @@
         <v>145</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>170</v>
@@ -2951,13 +2939,13 @@
         <v>132</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>168</v>
@@ -2977,13 +2965,13 @@
         <v>114</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>168</v>
@@ -3003,13 +2991,13 @@
         <v>114</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>168</v>
@@ -3029,13 +3017,13 @@
         <v>116</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>168</v>
@@ -3055,13 +3043,13 @@
         <v>116</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>168</v>
@@ -3081,13 +3069,13 @@
         <v>120</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>168</v>
@@ -3107,13 +3095,13 @@
         <v>116</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>168</v>
@@ -3133,13 +3121,13 @@
         <v>116</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>168</v>
@@ -3159,13 +3147,13 @@
         <v>116</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>168</v>
@@ -3185,13 +3173,13 @@
         <v>116</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>168</v>
@@ -3211,13 +3199,13 @@
         <v>118</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>132</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>168</v>
@@ -3237,13 +3225,13 @@
         <v>120</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>143</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>168</v>
@@ -3263,13 +3251,13 @@
         <v>161</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>163</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>165</v>
@@ -3289,13 +3277,13 @@
         <v>161</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>165</v>
@@ -3315,13 +3303,13 @@
         <v>148</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>178</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>165</v>
@@ -3341,13 +3329,13 @@
         <v>138</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>165</v>
@@ -3367,13 +3355,13 @@
         <v>123</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>261</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>165</v>
@@ -3393,13 +3381,13 @@
         <v>126</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>275</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>165</v>
@@ -3419,13 +3407,13 @@
         <v>132</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>163</v>
@@ -3445,13 +3433,13 @@
         <v>129</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>163</v>
@@ -3471,13 +3459,13 @@
         <v>116</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>163</v>
@@ -3497,13 +3485,13 @@
         <v>114</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>163</v>
@@ -3523,13 +3511,13 @@
         <v>143</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>165</v>
@@ -3549,13 +3537,13 @@
         <v>161</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>165</v>
@@ -3575,13 +3563,13 @@
         <v>168</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>165</v>
@@ -3601,13 +3589,13 @@
         <v>168</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>165</v>
@@ -3627,13 +3615,13 @@
         <v>168</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>168</v>
@@ -3653,13 +3641,13 @@
         <v>168</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>165</v>
@@ -3679,13 +3667,13 @@
         <v>168</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>165</v>
@@ -3705,13 +3693,13 @@
         <v>161</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>132</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>165</v>
@@ -3731,13 +3719,13 @@
         <v>158</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>165</v>
@@ -3757,13 +3745,13 @@
         <v>153</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>163</v>
@@ -3783,13 +3771,13 @@
         <v>153</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>163</v>
@@ -3809,13 +3797,13 @@
         <v>161</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>163</v>
@@ -3835,13 +3823,13 @@
         <v>173</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>163</v>
@@ -3861,13 +3849,13 @@
         <v>175</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>145</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>163</v>
@@ -3887,13 +3875,13 @@
         <v>168</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>148</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>161</v>
@@ -3913,13 +3901,13 @@
         <v>165</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>161</v>
@@ -3939,13 +3927,13 @@
         <v>161</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>161</v>
@@ -3965,13 +3953,13 @@
         <v>153</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>175</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>161</v>
@@ -3991,13 +3979,13 @@
         <v>150</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>161</v>
@@ -4017,13 +4005,13 @@
         <v>153</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>261</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>161</v>
@@ -4043,13 +4031,13 @@
         <v>224</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>287</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>161</v>
@@ -4069,13 +4057,13 @@
         <v>190</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>161</v>
@@ -4095,13 +4083,13 @@
         <v>198</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>106</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>161</v>
@@ -4121,13 +4109,13 @@
         <v>198</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>163</v>
@@ -4147,13 +4135,13 @@
         <v>190</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>163</v>
@@ -4173,13 +4161,13 @@
         <v>181</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>163</v>
@@ -4199,13 +4187,13 @@
         <v>163</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>163</v>
@@ -4225,13 +4213,13 @@
         <v>148</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>163</v>
@@ -4251,13 +4239,13 @@
         <v>145</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>163</v>
@@ -4277,13 +4265,13 @@
         <v>145</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>163</v>
@@ -4303,13 +4291,13 @@
         <v>148</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>163</v>
@@ -4329,13 +4317,13 @@
         <v>153</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>163</v>
@@ -4355,13 +4343,13 @@
         <v>156</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>163</v>
@@ -4381,13 +4369,13 @@
         <v>158</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>132</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>163</v>
@@ -4407,13 +4395,13 @@
         <v>161</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>161</v>
@@ -4433,13 +4421,13 @@
         <v>163</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>163</v>
@@ -4459,13 +4447,13 @@
         <v>173</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>163</v>
@@ -4485,13 +4473,13 @@
         <v>173</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>132</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>161</v>
@@ -4511,13 +4499,13 @@
         <v>165</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>161</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>161</v>
@@ -4537,13 +4525,13 @@
         <v>163</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>181</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>161</v>
@@ -4563,13 +4551,13 @@
         <v>156</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>165</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>161</v>
@@ -4589,13 +4577,13 @@
         <v>153</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>168</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>158</v>
@@ -4615,13 +4603,13 @@
         <v>150</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>334</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>158</v>
@@ -4641,13 +4629,13 @@
         <v>145</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>158</v>
@@ -4667,13 +4655,13 @@
         <v>145</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>161</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>158</v>
@@ -4693,13 +4681,13 @@
         <v>145</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>161</v>
@@ -4719,13 +4707,13 @@
         <v>153</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>161</v>
@@ -4745,13 +4733,13 @@
         <v>163</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>163</v>
@@ -4771,13 +4759,13 @@
         <v>173</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>163</v>
@@ -4797,13 +4785,13 @@
         <v>181</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>165</v>
@@ -4823,13 +4811,13 @@
         <v>170</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>165</v>
@@ -4849,13 +4837,13 @@
         <v>156</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>165</v>
@@ -4875,13 +4863,13 @@
         <v>148</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>165</v>
@@ -4901,13 +4889,13 @@
         <v>143</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>106</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>168</v>
@@ -4927,13 +4915,13 @@
         <v>143</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>168</v>
@@ -4953,13 +4941,13 @@
         <v>143</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>168</v>
@@ -4979,13 +4967,13 @@
         <v>135</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>165</v>
@@ -5005,13 +4993,13 @@
         <v>138</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>165</v>
@@ -5031,13 +5019,13 @@
         <v>143</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>165</v>
@@ -5057,13 +5045,13 @@
         <v>145</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>165</v>
@@ -5083,13 +5071,13 @@
         <v>236</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>165</v>
@@ -5109,13 +5097,13 @@
         <v>201</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>163</v>
@@ -5135,13 +5123,13 @@
         <v>175</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>161</v>
@@ -5161,13 +5149,13 @@
         <v>170</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>161</v>
@@ -5187,13 +5175,13 @@
         <v>170</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>161</v>
@@ -5213,13 +5201,13 @@
         <v>165</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>161</v>
@@ -5239,13 +5227,13 @@
         <v>165</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>409</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>161</v>
@@ -5265,13 +5253,13 @@
         <v>165</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>161</v>
@@ -5291,13 +5279,13 @@
         <v>165</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>161</v>
@@ -5317,13 +5305,13 @@
         <v>165</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>163</v>
@@ -5343,13 +5331,13 @@
         <v>173</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>165</v>
@@ -5369,13 +5357,13 @@
         <v>204</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>165</v>
@@ -5395,13 +5383,13 @@
         <v>228</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>165</v>
@@ -5421,13 +5409,13 @@
         <v>228</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>165</v>
@@ -5447,13 +5435,13 @@
         <v>221</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>165</v>
@@ -5473,13 +5461,13 @@
         <v>212</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>165</v>
@@ -5499,13 +5487,13 @@
         <v>168</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>163</v>
@@ -5525,13 +5513,13 @@
         <v>150</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>163</v>
@@ -5551,13 +5539,13 @@
         <v>145</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>163</v>
@@ -5577,13 +5565,13 @@
         <v>145</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>165</v>
@@ -5603,13 +5591,13 @@
         <v>153</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>163</v>
@@ -5629,13 +5617,13 @@
         <v>156</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>163</v>
@@ -5655,13 +5643,13 @@
         <v>156</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="H138" s="1" t="s">
         <v>161</v>
@@ -5681,13 +5669,13 @@
         <v>161</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>165</v>
@@ -5707,13 +5695,13 @@
         <v>163</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>150</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>161</v>
@@ -5733,13 +5721,13 @@
         <v>173</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>161</v>
@@ -5759,13 +5747,13 @@
         <v>170</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>158</v>
@@ -5785,13 +5773,13 @@
         <v>170</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>156</v>
@@ -5811,13 +5799,13 @@
         <v>165</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>170</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H144" s="1" t="s">
         <v>156</v>
@@ -5837,13 +5825,13 @@
         <v>168</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>161</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>158</v>
@@ -5863,13 +5851,13 @@
         <v>168</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>161</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>156</v>
@@ -5889,13 +5877,13 @@
         <v>168</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H147" s="1" t="s">
         <v>158</v>
@@ -5915,13 +5903,13 @@
         <v>158</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>148</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>165</v>
@@ -5941,13 +5929,13 @@
         <v>156</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>165</v>
@@ -5967,13 +5955,13 @@
         <v>158</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>170</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>165</v>
@@ -5993,13 +5981,13 @@
         <v>218</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>165</v>
@@ -6019,13 +6007,13 @@
         <v>212</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>168</v>
@@ -6045,13 +6033,13 @@
         <v>190</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>168</v>
@@ -6071,13 +6059,13 @@
         <v>173</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>168</v>
@@ -6097,13 +6085,13 @@
         <v>123</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H155" s="1" t="s">
         <v>165</v>
@@ -6123,13 +6111,13 @@
         <v>88</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>163</v>
@@ -6149,13 +6137,13 @@
         <v>82</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H157" s="1" t="s">
         <v>163</v>
@@ -6175,13 +6163,13 @@
         <v>67</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>161</v>
@@ -6201,13 +6189,13 @@
         <v>61</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>161</v>
@@ -6227,13 +6215,13 @@
         <v>64</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="H160" s="1" t="s">
         <v>158</v>
@@ -6253,13 +6241,13 @@
         <v>67</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="H161" s="1" t="s">
         <v>156</v>
@@ -6279,13 +6267,13 @@
         <v>67</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>123</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="H162" s="1" t="s">
         <v>153</v>
@@ -6305,13 +6293,13 @@
         <v>73</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>153</v>
@@ -6331,13 +6319,13 @@
         <v>76</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>132</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>153</v>
@@ -6357,13 +6345,13 @@
         <v>90</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>132</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>153</v>
@@ -6383,13 +6371,13 @@
         <v>79</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>132</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>153</v>
@@ -6409,13 +6397,13 @@
         <v>88</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>150</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>150</v>
@@ -6435,41 +6423,15 @@
         <v>90</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A169" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="H169" s="1" t="s">
         <v>150</v>
       </c>
     </row>
